--- a/Documentation/Best For Lists/Best Pets for Seniors with Vision Challenges List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Seniors with Vision Challenges List.xlsx
@@ -621,7 +621,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-12  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
+          <t>Generated: 2026-07-15  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best Pets for Seniors with Vision Challenges List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Seniors with Vision Challenges List.xlsx
@@ -1506,22 +1506,20 @@
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Budget Friendly</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Dog</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="n">
-        <v>25.99</v>
-      </c>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="n"/>
       <c r="G16" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14" t="n">
         <v>3</v>

--- a/Documentation/Best For Lists/Best Pets for Seniors with Vision Challenges List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Seniors with Vision Challenges List.xlsx
@@ -635,7 +635,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-16  |  Products shown: 11  |  Eliminated by dedup rule: 10  |  Pre-filter: Best For 1 not equal Children  (8 products removed)</t>
+          <t>Generated: 2026-08-10  |  Products shown: 11  |  Eliminated by dedup rule: 10  |  Pre-filter: Best For 1 not equal Children  (8 products removed)</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
         <v>4.5</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>11640</v>
+        <v>12310</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>4.2</v>
@@ -884,7 +884,7 @@
         <v>4.3</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>5164</v>
+        <v>5195</v>
       </c>
       <c r="I7" s="14" t="n">
         <v>4.2</v>
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="F8" s="9" t="n">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>5</v>
@@ -1010,13 +1010,13 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>456</v>
+        <v>29</v>
       </c>
       <c r="I9" s="14" t="n">
         <v>4.1</v>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="F10" s="9" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>5</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>4</v>
@@ -1142,13 +1142,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I11" s="14" t="n">
         <v>4</v>
@@ -1275,10 +1275,10 @@
         <v>349</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="I13" s="16" t="n">
         <v>3.6</v>
@@ -1408,7 +1408,7 @@
         <v>5</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="I15" s="17" t="n">
         <v>2.85</v>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="F16" s="9" t="n">
-        <v>359</v>
+        <v>319</v>
       </c>
       <c r="G16" s="9" t="n">
         <v>5</v>
@@ -1689,7 +1689,7 @@
         <v>4</v>
       </c>
       <c r="F5" s="20" t="n">
-        <v>4</v>
+        <v>4.95</v>
       </c>
       <c r="G5" s="20" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>score=4.00 rating=4</t>
+          <t>score=4.00 rating=4.95</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best Pets for Seniors with Vision Challenges List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Seniors with Vision Challenges List.xlsx
@@ -635,7 +635,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-08-10  |  Products shown: 11  |  Eliminated by dedup rule: 10  |  Pre-filter: Best For 1 not equal Children  (8 products removed)</t>
+          <t>Generated: 2026-08-13  |  Products shown: 11  |  Eliminated by dedup rule: 10  |  Pre-filter: Best For 1 not equal Children  (8 products removed)</t>
         </is>
       </c>
     </row>
